--- a/basedatos_partidas/salida/descompuestos/DRS010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/DRS010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A3:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -464,14 +464,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Demolición de pavimento cerámico existente y su capa de agarre.</t>
+          <t>Demolición de piso cerámico y su capa de pega.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demolición de pavimento existente de baldosa cerámica o de porcelanato y de su capa de agarre de mortero, ejecutada con martillo eléctrico manual, sin afectar a la losa ni a los elementos constructivos contiguos. Incluye protección previa de los paramentos y elementos que permanecen, control de polvo mediante aspiración, retirada manual de escombro en sacos hasta el punto de acopio y limpieza y barrido de la superficie resultante, dejándola preparada para recibir el nuevo soporte. No incluye el transporte a vertedero, que se valora en el capítulo de gestión de residuos. Medido en superficie realmente demolida.
+          <t xml:space="preserve">Demolición de piso existente de baldosa cerámica o de porcelanato, junto con su capa de pega de mortero, ejecutada con martillo eléctrico manual sin comprometer la losa ni los elementos constructivos vecinos. Incluye protección previa de paredes, puertas y ambientes contiguos, control de polvo mediante aspiración, retiro manual del escombro en sacos hasta el punto de acopio y barrido de la superficie resultante, dejándola lista para recibir el nuevo contrapiso. No incluye el bote del escombro, que se valora en el capítulo de gestión de residuos. Medido en superficie realmente demolida.
 </t>
         </is>
       </c>
@@ -546,204 +546,256 @@
       </c>
     </row>
     <row r="11">
-      <c r="F11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MT-CONS-DEM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Consumibles de demolición: puntas y cinceles de martillo, discos de corte y hojas de espátula.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MT-PROT-OBRA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Protección de obra con plástico, cartón corrugado y cinta de enmascarar.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Subtotal materiales:</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="H13" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MQ-MART-ELEC</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Martillo eléctrico de demolición de 5 kg, incluida amortización y consumo.</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>0.23</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G15" t="n">
         <v>3.9</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H15" t="n">
         <v>0.9</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>MQ-ASPIR</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Aspirador industrial con filtro de polvo fino para limpieza de soporte y control de polvo.</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F16" t="n">
         <v>0.12</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G16" t="n">
         <v>2.1</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="15">
-      <c r="F15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>Subtotal equipo y maquinaria:</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" t="n">
         <v>1.15</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="18">
+      <c r="A18" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>Mano de obra</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>MO-AYU-ESP</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Ayudante especializado.</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F19" t="n">
         <v>0.24</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H19" t="n">
         <v>0.96</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>MO-AYU</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Ayudante.</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
         <v>0.29</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" t="n">
         <v>3.5</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H20" t="n">
         <v>1.01</v>
       </c>
     </row>
-    <row r="19">
-      <c r="F19" s="1" t="inlineStr">
+    <row r="21">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Subtotal mano de obra:</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>1.97</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="D21" t="inlineStr">
+    <row r="23">
+      <c r="D23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G23" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.04</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="5" t="n">
-        <v>3.55</v>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="5" t="n">
+        <v>3.75</v>
       </c>
     </row>
   </sheetData>
